--- a/tumores/6. Laringe.xlsx
+++ b/tumores/6. Laringe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Ing.Salud\Practicas hospital ORL\clasificador-tnm-cabeza-cuello\tumores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DB9B5EF-E7CB-4C9E-80A5-C95274E59034}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A7111DE-9A0B-4957-A89E-D8B2E7BD7058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4CA4EF29-18F6-42B8-89A4-4F1C5D6105C8}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="125">
   <si>
     <t>T</t>
   </si>
@@ -202,24 +202,12 @@
     <t> Area poscricoidea, Espacio preepiglótico, Espacio paraglótico, Corteza interna del cartílago tiroides</t>
   </si>
   <si>
-    <t>Invasión:</t>
-  </si>
-  <si>
     <t>Invasión corteza externa del cartílago tiroides</t>
   </si>
   <si>
     <t>Tráquea, Músculo extrínseco profundo de la lengua, Músculos infrahioideos, Tiroides, Esófago</t>
   </si>
   <si>
-    <t>Invasión del espacio prevertebral</t>
-  </si>
-  <si>
-    <t>Atrapamiento de la arteria carótida</t>
-  </si>
-  <si>
-    <t>Invasión de estructuras mediastínicas</t>
-  </si>
-  <si>
     <t>Invasión fuera de laringe</t>
   </si>
   <si>
@@ -241,15 +229,9 @@
     <t>T1b</t>
   </si>
   <si>
-    <t>Deterioro de ambas cuerdas</t>
-  </si>
-  <si>
     <t>Ganglios linfáticos con ENE+ </t>
   </si>
   <si>
-    <t>Ganglio linfático con ENE+ </t>
-  </si>
-  <si>
     <t>T1, T1a, T1b, T2, T3</t>
   </si>
   <si>
@@ -271,36 +253,15 @@
     <t>🟥 T4a: Invasión de tejidos fuera de la laringe *</t>
   </si>
   <si>
-    <t>🟥 T4b: Invasión del espacio prevertebral</t>
-  </si>
-  <si>
-    <t>🟥 T4b: Atrapamiento de la arteria carótida</t>
-  </si>
-  <si>
-    <t>🟥 T4b: Invasión de estructuras mediastínicas</t>
-  </si>
-  <si>
     <t>🟩T1a: Limitado a una cuerda vocal (movilidad normal)</t>
   </si>
   <si>
-    <t>🟥T4b: Invasión del espacio prevertebral</t>
-  </si>
-  <si>
-    <t>🟥T4b: Invasión de estructuras mediastínicas</t>
-  </si>
-  <si>
-    <t>🟥T4b: Atrapamiento de la arteria carótida</t>
-  </si>
-  <si>
     <t>🟥T4a: Invasión corteza externa del cartílago tiroides</t>
   </si>
   <si>
     <t>🟦T3: Limitado a la laringe *</t>
   </si>
   <si>
-    <t>🟨T2: Deterioro de ambas cuerdas vocales + Diseminación *</t>
-  </si>
-  <si>
     <t>🟩T1b: Afectación de ambas cuerdas vocales (movilidad normal)</t>
   </si>
   <si>
@@ -337,9 +298,6 @@
     <t>🟦N3a: Un ganglio ipsilateral &gt;6 cm y ENE-</t>
   </si>
   <si>
-    <t>🟦N3b: Más de un ganglio con ENE+</t>
-  </si>
-  <si>
     <t>🟩N1: Un ganglio ipsilateral ≤3 cm y ENE-</t>
   </si>
   <si>
@@ -379,9 +337,6 @@
     <t>Afectación de ambas cuerdas vocales, mov. normal</t>
   </si>
   <si>
-    <t>Diseminación a supraglotis, Diseminación a subglotis</t>
-  </si>
-  <si>
     <t>🟨T2: Diseminación a una cuerda vocal *</t>
   </si>
   <si>
@@ -406,9 +361,6 @@
     <t>Múltiples ganglios ipsilaterales ≤6 cm y ENE-</t>
   </si>
   <si>
-    <t>🟦 N3b: Un ganglio con ENE+</t>
-  </si>
-  <si>
     <t>Múltiples ganglios ipsilateral ≤6 cm y ENE-</t>
   </si>
   <si>
@@ -422,6 +374,33 @@
   </si>
   <si>
     <t>Un ganglio ipsilateral &gt;3 cm , Múltiples ganglios, Un solo ganglio contralateral de cualquier tamaño</t>
+  </si>
+  <si>
+    <t>🟦N3b: Cualquier ganglio con ENE+</t>
+  </si>
+  <si>
+    <t>🟥 T4b: Enfermedad localmente muy avanzada *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invasión del espacio prevertebral,  Envuelve la carótida interna, Invasión de estructuras mediastínicas </t>
+  </si>
+  <si>
+    <t>🟦T3: Fijación de cuerdas con invasión especifica *</t>
+  </si>
+  <si>
+    <t>Fijación de cuerda + Inv:</t>
+  </si>
+  <si>
+    <t>Inv:</t>
+  </si>
+  <si>
+    <t>🟨T2: Diseminación y/o deterioro en movilidad *</t>
+  </si>
+  <si>
+    <t>Diseminación supraglotis, Diseminación subglotis, Fijación de cuerda vocal</t>
+  </si>
+  <si>
+    <t>Fijación de una cuerda vocal, Invasión del espacio paraglótico, Invasión de la cortical interna del cartílago tiroides</t>
   </si>
 </sst>
 </file>
@@ -478,7 +457,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -528,11 +507,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -571,6 +559,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -936,14 +927,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93349F43-C6E5-467C-91F1-9BFB47441F05}">
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.21875" style="1" customWidth="1"/>
     <col min="3" max="3" width="13.33203125" style="1" customWidth="1"/>
     <col min="4" max="4" width="35.33203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="27.88671875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="34.33203125" style="1" customWidth="1"/>
     <col min="6" max="6" width="27.21875" style="1" customWidth="1"/>
     <col min="7" max="7" width="38.44140625" style="1" customWidth="1"/>
     <col min="8" max="16384" width="11.5546875" style="1"/>
@@ -980,7 +971,7 @@
         <v>51</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>1</v>
@@ -997,7 +988,7 @@
         <v>51</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>2</v>
@@ -1014,7 +1005,7 @@
         <v>51</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>3</v>
@@ -1031,7 +1022,7 @@
         <v>51</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>4</v>
@@ -1048,7 +1039,7 @@
         <v>51</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>56</v>
@@ -1057,7 +1048,7 @@
         <v>4</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1068,16 +1059,16 @@
         <v>51</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>5</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>0</v>
       </c>
@@ -1085,7 +1076,7 @@
         <v>51</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>57</v>
@@ -1094,10 +1085,10 @@
         <v>5</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>0</v>
       </c>
@@ -1105,16 +1096,19 @@
         <v>51</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>88</v>
+        <v>119</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>57</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
@@ -1122,19 +1116,16 @@
         <v>51</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>0</v>
       </c>
@@ -1142,49 +1133,52 @@
         <v>51</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>81</v>
+        <v>74</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="F11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" s="9"/>
+      <c r="D12" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="F12" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G11" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>63</v>
+      <c r="G12" s="9"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -1195,16 +1189,16 @@
         <v>52</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>0</v>
       </c>
@@ -1212,13 +1206,13 @@
         <v>52</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1229,13 +1223,13 @@
         <v>52</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1246,16 +1240,16 @@
         <v>52</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>91</v>
+        <v>122</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>123</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>0</v>
       </c>
@@ -1263,19 +1257,19 @@
         <v>52</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>0</v>
       </c>
@@ -1283,19 +1277,16 @@
         <v>52</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>0</v>
       </c>
@@ -1303,108 +1294,111 @@
         <v>52</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>88</v>
+        <v>82</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="E21" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="F21" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>64</v>
-      </c>
+    </row>
+    <row r="21" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A21" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" s="9"/>
+      <c r="D21" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" s="9"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G22" s="1" t="s">
+      <c r="A22" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G23" s="1" t="s">
+    <row r="25" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A24" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="B25" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="G25" s="13" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F25" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>0</v>
       </c>
@@ -1412,16 +1406,19 @@
         <v>53</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>79</v>
+        <v>104</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>62</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>0</v>
       </c>
@@ -1429,16 +1426,19 @@
         <v>53</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>94</v>
+        <v>77</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>0</v>
       </c>
@@ -1446,19 +1446,16 @@
         <v>53</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>0</v>
       </c>
@@ -1466,304 +1463,303 @@
         <v>53</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="72" x14ac:dyDescent="0.3">
-      <c r="A30" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D30" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A30" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C30" s="9"/>
+      <c r="D30" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="E30" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G30" s="9"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B31" s="6"/>
+      <c r="C31" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B32" s="6"/>
+      <c r="C32" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A33" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B33" s="6"/>
+      <c r="C33" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A34" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B34" s="6"/>
+      <c r="C34" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D38" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="E30" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A31" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A34" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B36" s="6"/>
-      <c r="C36" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B37" s="6"/>
-      <c r="C37" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="E37" s="3"/>
-      <c r="F37" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A38" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B38" s="6"/>
-      <c r="C38" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="E38" s="3"/>
-      <c r="F38" s="3" t="s">
-        <v>19</v>
+      <c r="F38" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
         <v>14</v>
       </c>
       <c r="B39" s="6"/>
-      <c r="C39" s="3" t="s">
+      <c r="C39" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D39" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="E39" s="3"/>
-      <c r="F39" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="D39" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>15</v>
+      <c r="C40" s="11" t="s">
+        <v>16</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>122</v>
+        <v>83</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C41" s="1" t="s">
-        <v>15</v>
+      <c r="C41" s="11" t="s">
+        <v>16</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C42" s="1" t="s">
-        <v>15</v>
+      <c r="C42" s="11" t="s">
+        <v>16</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C43" s="1" t="s">
-        <v>15</v>
+      <c r="C43" s="11" t="s">
+        <v>16</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>102</v>
+        <v>91</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C44" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D44" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="E44" s="6"/>
-      <c r="F44" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G44" s="6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" s="6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B45" s="6"/>
-      <c r="C45" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D45" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="E45" s="6"/>
-      <c r="F45" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G45" s="6" t="s">
-        <v>72</v>
+      <c r="C44" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A45" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C45" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
@@ -1774,13 +1770,13 @@
         <v>16</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>25</v>
+        <v>113</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
@@ -1791,166 +1787,61 @@
         <v>16</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A48" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C48" s="11" t="s">
+      <c r="B48" s="4"/>
+      <c r="C48" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D48" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="D48" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C49" s="11" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>27</v>
+        <v>93</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C50" s="11" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>122</v>
+        <v>94</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A51" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C51" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C52" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A53" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C53" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B54" s="4"/>
-      <c r="C54" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="E54" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="F54" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G54" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A55" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A56" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G56" s="1" t="s">
         <v>38</v>
       </c>
     </row>
@@ -1985,7 +1876,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>18</v>
@@ -2027,7 +1918,7 @@
     </row>
     <row r="5" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>19</v>
@@ -2055,7 +1946,7 @@
     </row>
     <row r="7" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>48</v>

--- a/tumores/6. Laringe.xlsx
+++ b/tumores/6. Laringe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Ing.Salud\Practicas hospital ORL\clasificador-tnm-cabeza-cuello\tumores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A7111DE-9A0B-4957-A89E-D8B2E7BD7058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FA8C49A-23D3-4095-92C5-9FF53638F343}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4CA4EF29-18F6-42B8-89A4-4F1C5D6105C8}"/>
   </bookViews>

--- a/tumores/6. Laringe.xlsx
+++ b/tumores/6. Laringe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Ing.Salud\Practicas hospital ORL\clasificador-tnm-cabeza-cuello\tumores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FA8C49A-23D3-4095-92C5-9FF53638F343}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D446AC0-5061-4F40-A6FD-872763264BA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4CA4EF29-18F6-42B8-89A4-4F1C5D6105C8}"/>
   </bookViews>
@@ -265,9 +265,6 @@
     <t>🟩T1b: Afectación de ambas cuerdas vocales (movilidad normal)</t>
   </si>
   <si>
-    <t>🟦T3: Invasion especifica *</t>
-  </si>
-  <si>
     <t>🟨T2: Invasión en más de un subsitio</t>
   </si>
   <si>
@@ -385,9 +382,6 @@
     <t xml:space="preserve">Invasión del espacio prevertebral,  Envuelve la carótida interna, Invasión de estructuras mediastínicas </t>
   </si>
   <si>
-    <t>🟦T3: Fijación de cuerdas con invasión especifica *</t>
-  </si>
-  <si>
     <t>Fijación de cuerda + Inv:</t>
   </si>
   <si>
@@ -401,6 +395,12 @@
   </si>
   <si>
     <t>Fijación de una cuerda vocal, Invasión del espacio paraglótico, Invasión de la cortical interna del cartílago tiroides</t>
+  </si>
+  <si>
+    <t>🟦T3: Invasión específica *</t>
+  </si>
+  <si>
+    <t>🟦T3: Fijación de cuerdas con invasión específica *</t>
   </si>
 </sst>
 </file>
@@ -1005,7 +1005,7 @@
         <v>51</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>3</v>
@@ -1022,7 +1022,7 @@
         <v>51</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>4</v>
@@ -1039,7 +1039,7 @@
         <v>51</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>56</v>
@@ -1048,7 +1048,7 @@
         <v>4</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1059,13 +1059,13 @@
         <v>51</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>5</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
@@ -1076,7 +1076,7 @@
         <v>51</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>79</v>
+        <v>123</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>57</v>
@@ -1085,7 +1085,7 @@
         <v>5</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
@@ -1096,7 +1096,7 @@
         <v>51</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>57</v>
@@ -1105,7 +1105,7 @@
         <v>5</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1154,10 +1154,10 @@
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="E12" s="14" t="s">
         <v>117</v>
-      </c>
-      <c r="E12" s="14" t="s">
-        <v>118</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>13</v>
@@ -1212,7 +1212,7 @@
         <v>65</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1229,7 +1229,7 @@
         <v>66</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1240,10 +1240,10 @@
         <v>52</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>4</v>
@@ -1260,7 +1260,7 @@
         <v>77</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>5</v>
@@ -1294,7 +1294,7 @@
         <v>52</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>59</v>
@@ -1310,15 +1310,15 @@
       <c r="A21" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B21" s="9" t="s">
-        <v>51</v>
+      <c r="B21" s="1" t="s">
+        <v>52</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="E21" s="14" t="s">
         <v>117</v>
-      </c>
-      <c r="E21" s="14" t="s">
-        <v>118</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>13</v>
@@ -1369,7 +1369,7 @@
         <v>53</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>3</v>
@@ -1386,7 +1386,7 @@
         <v>53</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>62</v>
@@ -1395,7 +1395,7 @@
         <v>4</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1406,7 +1406,7 @@
         <v>53</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>62</v>
@@ -1415,7 +1415,7 @@
         <v>4</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
@@ -1463,7 +1463,7 @@
         <v>53</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>59</v>
@@ -1479,15 +1479,15 @@
       <c r="A30" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B30" s="9" t="s">
-        <v>51</v>
+      <c r="B30" s="1" t="s">
+        <v>53</v>
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="E30" s="14" t="s">
         <v>117</v>
-      </c>
-      <c r="E30" s="14" t="s">
-        <v>118</v>
       </c>
       <c r="F30" s="9" t="s">
         <v>13</v>
@@ -1503,7 +1503,7 @@
         <v>15</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3" t="s">
@@ -1522,7 +1522,7 @@
         <v>15</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3" t="s">
@@ -1541,7 +1541,7 @@
         <v>15</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E33" s="3"/>
       <c r="F33" s="3" t="s">
@@ -1560,7 +1560,7 @@
         <v>15</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3" t="s">
@@ -1578,13 +1578,13 @@
         <v>15</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1595,13 +1595,13 @@
         <v>15</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.3">
@@ -1629,7 +1629,7 @@
         <v>15</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>23</v>
@@ -1647,7 +1647,7 @@
         <v>15</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E39" s="6"/>
       <c r="F39" s="6" t="s">
@@ -1665,7 +1665,7 @@
         <v>16</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>17</v>
@@ -1682,7 +1682,7 @@
         <v>16</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>18</v>
@@ -1699,7 +1699,7 @@
         <v>16</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>19</v>
@@ -1716,7 +1716,7 @@
         <v>16</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>27</v>
@@ -1736,13 +1736,13 @@
         <v>16</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1753,13 +1753,13 @@
         <v>16</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
@@ -1770,13 +1770,13 @@
         <v>16</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
@@ -1787,13 +1787,13 @@
         <v>16</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>23</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -1805,10 +1805,10 @@
         <v>16</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F48" s="4" t="s">
         <v>24</v>
@@ -1822,7 +1822,7 @@
         <v>32</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>33</v>
@@ -1836,7 +1836,7 @@
         <v>32</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>34</v>

--- a/tumores/6. Laringe.xlsx
+++ b/tumores/6. Laringe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Ing.Salud\Practicas hospital ORL\clasificador-tnm-cabeza-cuello\tumores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D446AC0-5061-4F40-A6FD-872763264BA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E124E52-A6D0-4C89-80E5-8D8C973F12E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4CA4EF29-18F6-42B8-89A4-4F1C5D6105C8}"/>
   </bookViews>
@@ -259,9 +259,6 @@
     <t>🟥T4a: Invasión corteza externa del cartílago tiroides</t>
   </si>
   <si>
-    <t>🟦T3: Limitado a la laringe *</t>
-  </si>
-  <si>
     <t>🟩T1b: Afectación de ambas cuerdas vocales (movilidad normal)</t>
   </si>
   <si>
@@ -401,6 +398,9 @@
   </si>
   <si>
     <t>🟦T3: Fijación de cuerdas con invasión específica *</t>
+  </si>
+  <si>
+    <t>🟦T3: Limitado a la laringe (fijación y/o invasión) *</t>
   </si>
 </sst>
 </file>
@@ -1005,7 +1005,7 @@
         <v>51</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>3</v>
@@ -1022,7 +1022,7 @@
         <v>51</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>4</v>
@@ -1039,7 +1039,7 @@
         <v>51</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>56</v>
@@ -1048,7 +1048,7 @@
         <v>4</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1059,13 +1059,13 @@
         <v>51</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>5</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
@@ -1076,7 +1076,7 @@
         <v>51</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>57</v>
@@ -1085,7 +1085,7 @@
         <v>5</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
@@ -1096,7 +1096,7 @@
         <v>51</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>57</v>
@@ -1105,7 +1105,7 @@
         <v>5</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1154,10 +1154,10 @@
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="E12" s="14" t="s">
         <v>116</v>
-      </c>
-      <c r="E12" s="14" t="s">
-        <v>117</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>13</v>
@@ -1212,7 +1212,7 @@
         <v>65</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1223,13 +1223,13 @@
         <v>52</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>66</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1240,10 +1240,10 @@
         <v>52</v>
       </c>
       <c r="D17" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>121</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>4</v>
@@ -1257,10 +1257,10 @@
         <v>52</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>77</v>
+        <v>124</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>5</v>
@@ -1294,7 +1294,7 @@
         <v>52</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>59</v>
@@ -1315,10 +1315,10 @@
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="E21" s="14" t="s">
         <v>116</v>
-      </c>
-      <c r="E21" s="14" t="s">
-        <v>117</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>13</v>
@@ -1369,7 +1369,7 @@
         <v>53</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>3</v>
@@ -1386,7 +1386,7 @@
         <v>53</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>62</v>
@@ -1395,7 +1395,7 @@
         <v>4</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1406,7 +1406,7 @@
         <v>53</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>62</v>
@@ -1415,7 +1415,7 @@
         <v>4</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
@@ -1426,7 +1426,7 @@
         <v>53</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>77</v>
+        <v>124</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>63</v>
@@ -1463,7 +1463,7 @@
         <v>53</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>59</v>
@@ -1484,10 +1484,10 @@
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="E30" s="14" t="s">
         <v>116</v>
-      </c>
-      <c r="E30" s="14" t="s">
-        <v>117</v>
       </c>
       <c r="F30" s="9" t="s">
         <v>13</v>
@@ -1503,7 +1503,7 @@
         <v>15</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3" t="s">
@@ -1522,7 +1522,7 @@
         <v>15</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3" t="s">
@@ -1541,7 +1541,7 @@
         <v>15</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E33" s="3"/>
       <c r="F33" s="3" t="s">
@@ -1560,7 +1560,7 @@
         <v>15</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3" t="s">
@@ -1578,13 +1578,13 @@
         <v>15</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1595,13 +1595,13 @@
         <v>15</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.3">
@@ -1629,7 +1629,7 @@
         <v>15</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>23</v>
@@ -1647,7 +1647,7 @@
         <v>15</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E39" s="6"/>
       <c r="F39" s="6" t="s">
@@ -1665,7 +1665,7 @@
         <v>16</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>17</v>
@@ -1682,7 +1682,7 @@
         <v>16</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>18</v>
@@ -1699,7 +1699,7 @@
         <v>16</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>19</v>
@@ -1716,7 +1716,7 @@
         <v>16</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>27</v>
@@ -1736,13 +1736,13 @@
         <v>16</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1753,13 +1753,13 @@
         <v>16</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
@@ -1770,13 +1770,13 @@
         <v>16</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
@@ -1787,13 +1787,13 @@
         <v>16</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>23</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -1805,10 +1805,10 @@
         <v>16</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F48" s="4" t="s">
         <v>24</v>
@@ -1822,7 +1822,7 @@
         <v>32</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>33</v>
@@ -1836,7 +1836,7 @@
         <v>32</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>34</v>

--- a/tumores/6. Laringe.xlsx
+++ b/tumores/6. Laringe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Ing.Salud\Practicas hospital ORL\clasificador-tnm-cabeza-cuello\tumores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E124E52-A6D0-4C89-80E5-8D8C973F12E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EFC0B88-4F6C-469E-9F41-6788033647CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4CA4EF29-18F6-42B8-89A4-4F1C5D6105C8}"/>
   </bookViews>
@@ -199,12 +199,6 @@
     <t>Mucosa de la base de la lengua, Valécula, Pared media del seno piriforme</t>
   </si>
   <si>
-    <t> Area poscricoidea, Espacio preepiglótico, Espacio paraglótico, Corteza interna del cartílago tiroides</t>
-  </si>
-  <si>
-    <t>Invasión corteza externa del cartílago tiroides</t>
-  </si>
-  <si>
     <t>Tráquea, Músculo extrínseco profundo de la lengua, Músculos infrahioideos, Tiroides, Esófago</t>
   </si>
   <si>
@@ -217,9 +211,6 @@
     <t>Movilidad normal, Movilidad deteriorada</t>
   </si>
   <si>
-    <t>Fijación de una cuerda vocal, Invasión del espacio paraglótico, Invasión de la corteza interna del cartílago tiroides</t>
-  </si>
-  <si>
     <t>Limitado a laringe:</t>
   </si>
   <si>
@@ -256,9 +247,6 @@
     <t>🟩T1a: Limitado a una cuerda vocal (movilidad normal)</t>
   </si>
   <si>
-    <t>🟥T4a: Invasión corteza externa del cartílago tiroides</t>
-  </si>
-  <si>
     <t>🟩T1b: Afectación de ambas cuerdas vocales (movilidad normal)</t>
   </si>
   <si>
@@ -401,6 +389,18 @@
   </si>
   <si>
     <t>🟦T3: Limitado a la laringe (fijación y/o invasión) *</t>
+  </si>
+  <si>
+    <t>🟥T4a: Invasión cortical externa del cartílago tiroides</t>
+  </si>
+  <si>
+    <t>Invasión cortical externa del cartílago tiroides</t>
+  </si>
+  <si>
+    <t>Fijación de una cuerda vocal, Invasión del espacio paraglótico, Invasión de cortical interna del cartílago tiroides</t>
+  </si>
+  <si>
+    <t> Area post-cricoidea, Espacio preepiglótico, Espacio paraglótico, Cortical interna del cartílago tiroides</t>
   </si>
 </sst>
 </file>
@@ -971,7 +971,7 @@
         <v>51</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>1</v>
@@ -988,7 +988,7 @@
         <v>51</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>2</v>
@@ -1005,7 +1005,7 @@
         <v>51</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>3</v>
@@ -1022,7 +1022,7 @@
         <v>51</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>4</v>
@@ -1039,7 +1039,7 @@
         <v>51</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>56</v>
@@ -1048,7 +1048,7 @@
         <v>4</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1059,13 +1059,13 @@
         <v>51</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>5</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
@@ -1076,16 +1076,16 @@
         <v>51</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>57</v>
+        <v>124</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>5</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
@@ -1096,16 +1096,16 @@
         <v>51</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>57</v>
+        <v>124</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1116,13 +1116,13 @@
         <v>51</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>76</v>
+        <v>121</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>58</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
@@ -1133,16 +1133,16 @@
         <v>51</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
@@ -1154,10 +1154,10 @@
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="14" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>13</v>
@@ -1172,7 +1172,7 @@
         <v>52</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>1</v>
@@ -1189,7 +1189,7 @@
         <v>52</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>2</v>
@@ -1206,13 +1206,13 @@
         <v>52</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1223,13 +1223,13 @@
         <v>52</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1240,10 +1240,10 @@
         <v>52</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>4</v>
@@ -1257,16 +1257,16 @@
         <v>52</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>5</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1277,13 +1277,13 @@
         <v>52</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>76</v>
+        <v>121</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>58</v>
+        <v>122</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
@@ -1294,16 +1294,16 @@
         <v>52</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
@@ -1315,10 +1315,10 @@
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="14" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>13</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="C22" s="13"/>
       <c r="D22" s="13" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E22" s="13"/>
       <c r="F22" s="13" t="s">
@@ -1352,7 +1352,7 @@
         <v>53</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>2</v>
@@ -1369,13 +1369,13 @@
         <v>53</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
@@ -1386,16 +1386,16 @@
         <v>53</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1406,16 +1406,16 @@
         <v>53</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
@@ -1426,16 +1426,16 @@
         <v>53</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>63</v>
+        <v>123</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>5</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1446,13 +1446,13 @@
         <v>53</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>76</v>
+        <v>121</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>58</v>
+        <v>122</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
@@ -1463,16 +1463,16 @@
         <v>53</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
@@ -1484,10 +1484,10 @@
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="14" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F30" s="9" t="s">
         <v>13</v>
@@ -1503,7 +1503,7 @@
         <v>15</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3" t="s">
@@ -1522,7 +1522,7 @@
         <v>15</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3" t="s">
@@ -1541,7 +1541,7 @@
         <v>15</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E33" s="3"/>
       <c r="F33" s="3" t="s">
@@ -1560,7 +1560,7 @@
         <v>15</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3" t="s">
@@ -1578,13 +1578,13 @@
         <v>15</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1595,13 +1595,13 @@
         <v>15</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.3">
@@ -1629,7 +1629,7 @@
         <v>15</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>23</v>
@@ -1647,14 +1647,14 @@
         <v>15</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E39" s="6"/>
       <c r="F39" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
@@ -1665,7 +1665,7 @@
         <v>16</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>17</v>
@@ -1682,7 +1682,7 @@
         <v>16</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>18</v>
@@ -1699,7 +1699,7 @@
         <v>16</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>19</v>
@@ -1716,7 +1716,7 @@
         <v>16</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>27</v>
@@ -1725,7 +1725,7 @@
         <v>20</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1736,13 +1736,13 @@
         <v>16</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1753,13 +1753,13 @@
         <v>16</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
@@ -1770,13 +1770,13 @@
         <v>16</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
@@ -1787,13 +1787,13 @@
         <v>16</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>23</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -1805,10 +1805,10 @@
         <v>16</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F48" s="4" t="s">
         <v>24</v>
@@ -1822,7 +1822,7 @@
         <v>32</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>33</v>
@@ -1836,7 +1836,7 @@
         <v>32</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>34</v>
@@ -1876,7 +1876,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>18</v>
@@ -1918,7 +1918,7 @@
     </row>
     <row r="5" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>19</v>
@@ -1946,7 +1946,7 @@
     </row>
     <row r="7" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>48</v>

--- a/tumores/6. Laringe.xlsx
+++ b/tumores/6. Laringe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Ing.Salud\Practicas hospital ORL\clasificador-tnm-cabeza-cuello\tumores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EFC0B88-4F6C-469E-9F41-6788033647CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7C5E802-47EE-431B-A561-A4FB094B9E4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4CA4EF29-18F6-42B8-89A4-4F1C5D6105C8}"/>
   </bookViews>
